--- a/Modelo dos motores/Zona morta.xlsx
+++ b/Modelo dos motores/Zona morta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9d271107c381e32d/MEF/1.º ano/2.º semestre/Robótica/Projeto 2 - carrinho/Código/Modelo dos motores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{EB52BC16-3578-0B4F-8C6B-6F76DD5E3988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55860415-3503-4AF8-8FC4-5EB1918FAE9D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{941B25EE-ABF3-4DB7-A382-19C93C27BA75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{F56D46C1-57AD-7E43-8DEC-B194DF26C3A3}"/>
+    <workbookView xWindow="2628" yWindow="3720" windowWidth="17280" windowHeight="9960" activeTab="3" xr2:uid="{F56D46C1-57AD-7E43-8DEC-B194DF26C3A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Motor1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="12">
   <si>
     <t>w_ground</t>
   </si>
@@ -69,6 +69,15 @@
   </si>
   <si>
     <t>neg</t>
+  </si>
+  <si>
+    <t>w_ar</t>
+  </si>
+  <si>
+    <t>w_solo</t>
+  </si>
+  <si>
+    <t>V</t>
   </si>
 </sst>
 </file>
@@ -5110,10 +5119,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
@@ -5824,13 +5829,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -5955,13 +5960,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
